--- a/docs/mapping.xlsx
+++ b/docs/mapping.xlsx
@@ -1395,7 +1395,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>branche 7 — exclusif, première correspondance</t>
+          <t>branche 7 — exclusif, première correspondance ; motif : OSM n'a pas de valeur consensuelle pour ces lieux-dits bâtis, et la source ne dit pas s'il s'agit d'un moulin à vent ou à eau : on reste sur le toponyme, nature conservée.</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>branche 8 — exclusif, première correspondance</t>
+          <t>branche 8 — exclusif, première correspondance ; motif : « Lieu-dit habité » : `importance` est le seul critère de hiérarchie disponible. Calibration à relire : elle décide de ce qui s'affiche comme village ou comme écart.</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>branche 8 — exclusif, première correspondance</t>
+          <t>branche 8 — exclusif, première correspondance ; motif : « Lieu-dit habité » : `importance` est le seul critère de hiérarchie disponible. Calibration à relire : elle décide de ce qui s'affiche comme village ou comme écart.</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>branche 8 — exclusif, première correspondance</t>
+          <t>branche 8 — exclusif, première correspondance ; motif : « Lieu-dit habité » : `importance` est le seul critère de hiérarchie disponible. Calibration à relire : elle décide de ce qui s'affiche comme village ou comme écart.</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>branche 8 — exclusif, première correspondance</t>
+          <t>branche 8 — exclusif, première correspondance ; motif : « Lieu-dit habité » : `importance` est le seul critère de hiérarchie disponible. Calibration à relire : elle décide de ce qui s'affiche comme village ou comme écart.</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>branche 8 — exclusif, première correspondance</t>
+          <t>branche 8 — exclusif, première correspondance ; motif : « Lieu-dit habité » : `importance` est le seul critère de hiérarchie disponible. Calibration à relire : elle décide de ce qui s'affiche comme village ou comme écart.</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>branche 8 — exclusif, première correspondance</t>
+          <t>branche 8 — exclusif, première correspondance ; motif : « Lieu-dit habité » : `importance` est le seul critère de hiérarchie disponible. Calibration à relire : elle décide de ce qui s'affiche comme village ou comme écart.</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>branche 8 — exclusif, première correspondance</t>
+          <t>branche 8 — exclusif, première correspondance ; motif : « Lieu-dit habité » : `importance` est le seul critère de hiérarchie disponible. Calibration à relire : elle décide de ce qui s'affiche comme village ou comme écart.</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>branche 18 — exclusif, première correspondance</t>
+          <t>branche 18 — exclusif, première correspondance ; motif : `caravan_site` est l'usage OSM français pour ces aires, malgré l'ambiguïté du terme touristique.</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>branche 18 — exclusif, première correspondance</t>
+          <t>branche 18 — exclusif, première correspondance ; motif : `caravan_site` est l'usage OSM français pour ces aires, malgré l'ambiguïté du terme touristique.</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>branche 59 — exclusif, première correspondance</t>
+          <t>branche 59 — exclusif, première correspondance ; motif : En milieu rural ces salles sont le plus souvent des salles des fêtes : `community_centre` plutôt que `theatre`.</t>
         </is>
       </c>
     </row>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>branche 62 — exclusif, première correspondance</t>
+          <t>branche 62 — exclusif, première correspondance ; motif : Nature sans correspondance OSM assumée : `fixme` est un vrai tag, lu par les éditeurs et les outils de contrôle — préférable à un `tourism=attraction` posé au jugé.</t>
         </is>
       </c>
     </row>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>branche 7 — exclusif, première correspondance</t>
+          <t>branche 7 — exclusif, première correspondance ; motif : 739 entités, toutes « Borne de rechargement électrique » d'après `nature_detaillee` ; la source Etalab (opérateurs IRVE) le confirme.</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>branche 7 — exclusif, première correspondance</t>
+          <t>branche 7 — exclusif, première correspondance ; motif : 739 entités, toutes « Borne de rechargement électrique » d'après `nature_detaillee` ; la source Etalab (opérateurs IRVE) le confirme.</t>
         </is>
       </c>
     </row>
@@ -7807,7 +7807,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>branche 1 — exclusif, première correspondance</t>
+          <t>branche 1 — exclusif, première correspondance ; motif : Réservoir surélevé : `man_made=water_tower` ; c'est aussi un bâtiment.</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>branche 1 — exclusif, première correspondance</t>
+          <t>branche 1 — exclusif, première correspondance ; motif : Réservoir surélevé : `man_made=water_tower` ; c'est aussi un bâtiment.</t>
         </is>
       </c>
     </row>
@@ -12159,7 +12159,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>branche 1 — exclusif, première correspondance</t>
+          <t>branche 1 — exclusif, première correspondance ; motif : La restriction décrit ce qu'EST la voie — un aménagement cyclable propre — pas une contrainte qui s'y ajoute. Elle prime donc sur la nature.</t>
         </is>
       </c>
     </row>
@@ -12321,7 +12321,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>branche 6 — exclusif, première correspondance</t>
+          <t>branche 6 — exclusif, première correspondance ; motif : « Chemin » BD Topo : prévu pour les véhicules ou engins d'exploitation, pas forcément carrossable par tous les temps — c'est la définition d'un `track`.</t>
         </is>
       </c>
     </row>
@@ -12348,7 +12348,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>branche 6 — exclusif, première correspondance</t>
+          <t>branche 6 — exclusif, première correspondance ; motif : « Chemin » BD Topo : prévu pour les véhicules ou engins d'exploitation, pas forcément carrossable par tous les temps — c'est la définition d'un `track`.</t>
         </is>
       </c>
     </row>
@@ -12375,7 +12375,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>branche 7 — exclusif, première correspondance</t>
+          <t>branche 7 — exclusif, première correspondance ; motif : Carrossable et publique selon la source (13 privées sur 56 369 dans la Vienne, 54 502 en accès libre) : donc `unclassified`, pas `track`, qui sous-entendrait un usage agricole non établi. Le revêtement est porté par `surface`, requalifiable.</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>branche 7 — exclusif, première correspondance</t>
+          <t>branche 7 — exclusif, première correspondance ; motif : Carrossable et publique selon la source (13 privées sur 56 369 dans la Vienne, 54 502 en accès libre) : donc `unclassified`, pas `track`, qui sous-entendrait un usage agricole non établi. Le revêtement est porté par `surface`, requalifiable.</t>
         </is>
       </c>
     </row>
@@ -12429,7 +12429,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>branche 8 — exclusif, première correspondance ; si nature = Bretelle</t>
+          <t>branche 8 — exclusif, première correspondance ; motif : La BD Topo ne dit pas quelle route la bretelle raccorde ; la classe est déduite de `importance`. IGN affecte à une bretelle « l'importance la moins importante des deux tronçons qu'elle joint ». Approximation à remplacer par une propagation depuis les tronçons connectés. ; si nature = Bretelle</t>
         </is>
       </c>
     </row>
@@ -12456,7 +12456,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>branche 8 — exclusif, première correspondance ; si nature = Bretelle</t>
+          <t>branche 8 — exclusif, première correspondance ; motif : La BD Topo ne dit pas quelle route la bretelle raccorde ; la classe est déduite de `importance`. IGN affecte à une bretelle « l'importance la moins importante des deux tronçons qu'elle joint ». Approximation à remplacer par une propagation depuis les tronçons connectés. ; si nature = Bretelle</t>
         </is>
       </c>
     </row>
@@ -12483,7 +12483,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>branche 8 — exclusif, première correspondance ; si nature = Bretelle</t>
+          <t>branche 8 — exclusif, première correspondance ; motif : La BD Topo ne dit pas quelle route la bretelle raccorde ; la classe est déduite de `importance`. IGN affecte à une bretelle « l'importance la moins importante des deux tronçons qu'elle joint ». Approximation à remplacer par une propagation depuis les tronçons connectés. ; si nature = Bretelle</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>branche 8 — exclusif, première correspondance ; si nature = Bretelle</t>
+          <t>branche 8 — exclusif, première correspondance ; motif : La BD Topo ne dit pas quelle route la bretelle raccorde ; la classe est déduite de `importance`. IGN affecte à une bretelle « l'importance la moins importante des deux tronçons qu'elle joint ». Approximation à remplacer par une propagation depuis les tronçons connectés. ; si nature = Bretelle</t>
         </is>
       </c>
     </row>
@@ -12537,7 +12537,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>branche 8 — exclusif, première correspondance ; si nature = Bretelle</t>
+          <t>branche 8 — exclusif, première correspondance ; motif : La BD Topo ne dit pas quelle route la bretelle raccorde ; la classe est déduite de `importance`. IGN affecte à une bretelle « l'importance la moins importante des deux tronçons qu'elle joint ». Approximation à remplacer par une propagation depuis les tronçons connectés. ; si nature = Bretelle</t>
         </is>
       </c>
     </row>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>branche 8 — exclusif, première correspondance ; si nature = Bretelle</t>
+          <t>branche 8 — exclusif, première correspondance ; motif : La BD Topo ne dit pas quelle route la bretelle raccorde ; la classe est déduite de `importance`. IGN affecte à une bretelle « l'importance la moins importante des deux tronçons qu'elle joint ». Approximation à remplacer par une propagation depuis les tronçons connectés. ; si nature = Bretelle</t>
         </is>
       </c>
     </row>
@@ -12591,7 +12591,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>branche 8 — exclusif, première correspondance ; si nature = Bretelle</t>
+          <t>branche 8 — exclusif, première correspondance ; motif : La BD Topo ne dit pas quelle route la bretelle raccorde ; la classe est déduite de `importance`. IGN affecte à une bretelle « l'importance la moins importante des deux tronçons qu'elle joint ». Approximation à remplacer par une propagation depuis les tronçons connectés. ; si nature = Bretelle</t>
         </is>
       </c>
     </row>
@@ -12618,7 +12618,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>branche 9 — exclusif, première correspondance</t>
+          <t>branche 9 — exclusif, première correspondance ; motif : `junction=roundabout` est une forme, pas une classe : la classe vient de `importance`, à défaut de connaître la route la plus importante qui aboutit à l'anneau.</t>
         </is>
       </c>
     </row>
@@ -12645,7 +12645,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>branche 9 — exclusif, première correspondance</t>
+          <t>branche 9 — exclusif, première correspondance ; motif : `junction=roundabout` est une forme, pas une classe : la classe vient de `importance`, à défaut de connaître la route la plus importante qui aboutit à l'anneau.</t>
         </is>
       </c>
     </row>
@@ -12672,7 +12672,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>branche 9 — exclusif, première correspondance ; si nature = Rond-point</t>
+          <t>branche 9 — exclusif, première correspondance ; motif : `junction=roundabout` est une forme, pas une classe : la classe vient de `importance`, à défaut de connaître la route la plus importante qui aboutit à l'anneau. ; si nature = Rond-point</t>
         </is>
       </c>
     </row>
@@ -12699,7 +12699,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>branche 9 — exclusif, première correspondance ; si nature = Rond-point</t>
+          <t>branche 9 — exclusif, première correspondance ; motif : `junction=roundabout` est une forme, pas une classe : la classe vient de `importance`, à défaut de connaître la route la plus importante qui aboutit à l'anneau. ; si nature = Rond-point</t>
         </is>
       </c>
     </row>
@@ -12726,7 +12726,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>branche 9 — exclusif, première correspondance ; si nature = Rond-point</t>
+          <t>branche 9 — exclusif, première correspondance ; motif : `junction=roundabout` est une forme, pas une classe : la classe vient de `importance`, à défaut de connaître la route la plus importante qui aboutit à l'anneau. ; si nature = Rond-point</t>
         </is>
       </c>
     </row>
@@ -12753,7 +12753,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>branche 9 — exclusif, première correspondance ; si nature = Rond-point</t>
+          <t>branche 9 — exclusif, première correspondance ; motif : `junction=roundabout` est une forme, pas une classe : la classe vient de `importance`, à défaut de connaître la route la plus importante qui aboutit à l'anneau. ; si nature = Rond-point</t>
         </is>
       </c>
     </row>
@@ -12780,7 +12780,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>branche 9 — exclusif, première correspondance ; si nature = Rond-point</t>
+          <t>branche 9 — exclusif, première correspondance ; motif : `junction=roundabout` est une forme, pas une classe : la classe vient de `importance`, à défaut de connaître la route la plus importante qui aboutit à l'anneau. ; si nature = Rond-point</t>
         </is>
       </c>
     </row>
@@ -12807,7 +12807,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>branche 9 — exclusif, première correspondance ; si nature = Rond-point</t>
+          <t>branche 9 — exclusif, première correspondance ; motif : `junction=roundabout` est une forme, pas une classe : la classe vient de `importance`, à défaut de connaître la route la plus importante qui aboutit à l'anneau. ; si nature = Rond-point</t>
         </is>
       </c>
     </row>
@@ -12834,7 +12834,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>branche 9 — exclusif, première correspondance ; si nature = Rond-point</t>
+          <t>branche 9 — exclusif, première correspondance ; motif : `junction=roundabout` est une forme, pas une classe : la classe vient de `importance`, à défaut de connaître la route la plus importante qui aboutit à l'anneau. ; si nature = Rond-point</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>branche 10 — exclusif, première correspondance</t>
+          <t>branche 10 — exclusif, première correspondance ; motif : Le classement administratif fait autorité quand il est renseigné (15,7 % des tronçons de la Vienne).</t>
         </is>
       </c>
     </row>
@@ -12942,7 +12942,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>branche 13 — exclusif, première correspondance ; si cpx_classement_administratif contient « Départementale »</t>
+          <t>branche 13 — exclusif, première correspondance ; motif : Départementale : la classe suit `importance`, qu'IGN définit comme une hiérarchisation fonctionnelle du réseau (non administrative). Mesuré : importance 4 = 29 790 D sur 34 022 tronçons. ; si cpx_classement_administratif contient « Départementale »</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>branche 13 — exclusif, première correspondance ; si cpx_classement_administratif contient « Départementale »</t>
+          <t>branche 13 — exclusif, première correspondance ; motif : Départementale : la classe suit `importance`, qu'IGN définit comme une hiérarchisation fonctionnelle du réseau (non administrative). Mesuré : importance 4 = 29 790 D sur 34 022 tronçons. ; si cpx_classement_administratif contient « Départementale »</t>
         </is>
       </c>
     </row>
@@ -12996,7 +12996,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>branche 13 — exclusif, première correspondance ; si cpx_classement_administratif contient « Départementale »</t>
+          <t>branche 13 — exclusif, première correspondance ; motif : Départementale : la classe suit `importance`, qu'IGN définit comme une hiérarchisation fonctionnelle du réseau (non administrative). Mesuré : importance 4 = 29 790 D sur 34 022 tronçons. ; si cpx_classement_administratif contient « Départementale »</t>
         </is>
       </c>
     </row>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>branche 13 — exclusif, première correspondance ; si cpx_classement_administratif contient « Départementale »</t>
+          <t>branche 13 — exclusif, première correspondance ; motif : Départementale : la classe suit `importance`, qu'IGN définit comme une hiérarchisation fonctionnelle du réseau (non administrative). Mesuré : importance 4 = 29 790 D sur 34 022 tronçons. ; si cpx_classement_administratif contient « Départementale »</t>
         </is>
       </c>
     </row>
@@ -13050,7 +13050,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>branche 13 — exclusif, première correspondance ; si cpx_classement_administratif contient « Départementale »</t>
+          <t>branche 13 — exclusif, première correspondance ; motif : Départementale : la classe suit `importance`, qu'IGN définit comme une hiérarchisation fonctionnelle du réseau (non administrative). Mesuré : importance 4 = 29 790 D sur 34 022 tronçons. ; si cpx_classement_administratif contient « Départementale »</t>
         </is>
       </c>
     </row>
@@ -13077,7 +13077,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>branche 13 — exclusif, première correspondance ; si cpx_classement_administratif contient « Départementale »</t>
+          <t>branche 13 — exclusif, première correspondance ; motif : Départementale : la classe suit `importance`, qu'IGN définit comme une hiérarchisation fonctionnelle du réseau (non administrative). Mesuré : importance 4 = 29 790 D sur 34 022 tronçons. ; si cpx_classement_administratif contient « Départementale »</t>
         </is>
       </c>
     </row>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>branche 13 — exclusif, première correspondance ; si cpx_classement_administratif contient « Départementale »</t>
+          <t>branche 13 — exclusif, première correspondance ; motif : Départementale : la classe suit `importance`, qu'IGN définit comme une hiérarchisation fonctionnelle du réseau (non administrative). Mesuré : importance 4 = 29 790 D sur 34 022 tronçons. ; si cpx_classement_administratif contient « Départementale »</t>
         </is>
       </c>
     </row>
@@ -13131,7 +13131,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>branche 14 — exclusif, première correspondance</t>
+          <t>branche 14 — exclusif, première correspondance ; motif : Type autoroutier sans classement Autoroute : le préfixe du numéro tranche (A10 → motorway ; N147 en voie express → trunk).</t>
         </is>
       </c>
     </row>
@@ -13374,7 +13374,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>branche 17 — exclusif, première correspondance</t>
+          <t>branche 17 — exclusif, première correspondance ; motif : Importance 5 = desserte locale (129 135 tronçons, le gros du réseau). `urbain` sépare la voirie de lotissement (`residential`) de la voie communale rase-campagne (`unclassified`).</t>
         </is>
       </c>
     </row>
@@ -13401,7 +13401,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>branche 18 — exclusif, première correspondance ; si nature = Route à 1 chaussée</t>
+          <t>branche 18 — exclusif, première correspondance ; motif : Repli nature × importance pour les 84,3 % de tronçons sans classement administratif. ; si nature = Route à 1 chaussée</t>
         </is>
       </c>
     </row>
@@ -13428,7 +13428,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>branche 18 — exclusif, première correspondance ; si nature = Route à 1 chaussée</t>
+          <t>branche 18 — exclusif, première correspondance ; motif : Repli nature × importance pour les 84,3 % de tronçons sans classement administratif. ; si nature = Route à 1 chaussée</t>
         </is>
       </c>
     </row>
@@ -13455,7 +13455,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>branche 18 — exclusif, première correspondance ; si nature = Route à 1 chaussée</t>
+          <t>branche 18 — exclusif, première correspondance ; motif : Repli nature × importance pour les 84,3 % de tronçons sans classement administratif. ; si nature = Route à 1 chaussée</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>branche 18 — exclusif, première correspondance ; si nature = Route à 1 chaussée</t>
+          <t>branche 18 — exclusif, première correspondance ; motif : Repli nature × importance pour les 84,3 % de tronçons sans classement administratif. ; si nature = Route à 1 chaussée</t>
         </is>
       </c>
     </row>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>branche 18 — exclusif, première correspondance ; si nature = Route à 1 chaussée</t>
+          <t>branche 18 — exclusif, première correspondance ; motif : Repli nature × importance pour les 84,3 % de tronçons sans classement administratif. ; si nature = Route à 1 chaussée</t>
         </is>
       </c>
     </row>
@@ -13536,7 +13536,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>branche 18 — exclusif, première correspondance ; si nature = Route à 1 chaussée</t>
+          <t>branche 18 — exclusif, première correspondance ; motif : Repli nature × importance pour les 84,3 % de tronçons sans classement administratif. ; si nature = Route à 1 chaussée</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>branche 18 — exclusif, première correspondance ; si nature = Route à 1 chaussée</t>
+          <t>branche 18 — exclusif, première correspondance ; motif : Repli nature × importance pour les 84,3 % de tronçons sans classement administratif. ; si nature = Route à 1 chaussée</t>
         </is>
       </c>
     </row>
@@ -17068,7 +17068,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>branche 2 — exclusif, première correspondance</t>
+          <t>branche 2 — exclusif, première correspondance ; motif : Un bois nommé reste un toponyme : son emprise, quand elle existe, est portée par `zone_de_vegetation`. `natural=wood` sur un point dupliquerait l'information.</t>
         </is>
       </c>
     </row>
@@ -20274,7 +20274,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>branche 1 — exclusif, première correspondance</t>
+          <t>branche 1 — exclusif, première correspondance ; motif : Un fossé reste un fossé quelle que soit sa largeur : la nature de l'ouvrage l'emporte sur la classe dimensionnelle.</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>branche 4 — exclusif, première correspondance</t>
+          <t>branche 4 — exclusif, première correspondance ; motif : `classe_de_largeur` est le seul critère dimensionnel disponible ; le seuil OSM usuel entre `stream` et `river` (≈ 5 m) tombe exactement sur une borne de la nomenclature IGN.</t>
         </is>
       </c>
     </row>
@@ -20434,7 +20434,11 @@
           <t>culvert</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>motif : Écoulement busé sous un remblai ou une voirie : `tunnel=culvert`.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -20457,7 +20461,11 @@
           <t>-1</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>motif : Écoulement busé sous un remblai ou une voirie : `tunnel=culvert`.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -25254,7 +25262,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>branche 14 — exclusif, première correspondance</t>
+          <t>branche 14 — exclusif, première correspondance ; motif : 229 978 bâtiments résidentiels à exactement 1 logement dans la Vienne : `nombre_de_logements` étaye solidement la distinction maison / immeuble.</t>
         </is>
       </c>
     </row>
@@ -25281,7 +25289,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>branche 15 — exclusif, première correspondance</t>
+          <t>branche 15 — exclusif, première correspondance ; motif : Plusieurs logements dans un bâtiment résidentiel : immeuble.</t>
         </is>
       </c>
     </row>
@@ -25335,7 +25343,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>branche 17 — exclusif, première correspondance</t>
+          <t>branche 17 — exclusif, première correspondance ; motif : OSM n'a pas de valeur consensuelle pour « annexe » (garages, remises, abris confondus) ; `construction_legere` isole au moins les abris légers.</t>
         </is>
       </c>
     </row>
@@ -25362,7 +25370,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>branche 18 — exclusif, première correspondance</t>
+          <t>branche 18 — exclusif, première correspondance ; motif : Annexe sans autre précision : `building=yes` avec l'usage source conservé, plutôt qu'une valeur inventée.</t>
         </is>
       </c>
     </row>
@@ -25524,7 +25532,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>branche 24 — exclusif, première correspondance</t>
+          <t>branche 24 — exclusif, première correspondance ; motif : La nature exclut le résidentiel mais ne tranche pas entre trois fonctions aux valeurs OSM distinctes : en choisir une serait fabriquer de l'information. La nature source est conservée, requalifiable.</t>
         </is>
       </c>
     </row>
@@ -25558,12 +25566,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>nature, usage_1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>(nature ∈ {Eglise, Chapelle}) et (usage_1 = Religieux)</t>
+          <t>(toujours)</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -25576,17 +25584,21 @@
           <t>place_of_worship</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>motif : `nature` donne la forme du bâtiment, `usage_1` atteste l'usage courant : c'est leur conjonction qui justifie `amenity=place_of_worship`, pas la forme seule. all_of: - {nature: [Eglise, Chapelle]} - {usage_1: Religieux}</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>nature, usage_1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>(nature ∈ {Eglise, Chapelle}) et (usage_1 = Religieux)</t>
+          <t>(toujours)</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -25599,7 +25611,11 @@
           <t>christian</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>motif : `nature` donne la forme du bâtiment, `usage_1` atteste l'usage courant : c'est leur conjonction qui justifie `amenity=place_of_worship`, pas la forme seule. all_of: - {nature: [Eglise, Chapelle]} - {usage_1: Religieux}</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -28543,7 +28559,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>branche 3 — exclusif, première correspondance</t>
+          <t>branche 3 — exclusif, première correspondance ; motif : Plantation exploitée : `landuse=forest` plutôt que `natural=wood`, qui suggère un boisement spontané.</t>
         </is>
       </c>
     </row>
@@ -28570,7 +28586,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>branche 3 — exclusif, première correspondance</t>
+          <t>branche 3 — exclusif, première correspondance ; motif : Plantation exploitée : `landuse=forest` plutôt que `natural=wood`, qui suggère un boisement spontané.</t>
         </is>
       </c>
     </row>
@@ -28624,7 +28640,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>branche 5 — exclusif, première correspondance</t>
+          <t>branche 5 — exclusif, première correspondance ; motif : Couvert discontinu, plus proche du fourré que du bois.</t>
         </is>
       </c>
     </row>
@@ -29534,7 +29550,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>branche 5 — exclusif, première correspondance</t>
+          <t>branche 5 — exclusif, première correspondance ; motif : Bassin technique : `landuse=basin` décrit l'ouvrage, `natural=water` décrirait l'eau — ici c'est l'ouvrage qui est cartographié.</t>
         </is>
       </c>
     </row>
@@ -29561,7 +29577,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>branche 5 — exclusif, première correspondance</t>
+          <t>branche 5 — exclusif, première correspondance ; motif : Bassin technique : `landuse=basin` décrit l'ouvrage, `natural=water` décrirait l'eau — ici c'est l'ouvrage qui est cartographié.</t>
         </is>
       </c>
     </row>
@@ -29723,7 +29739,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>branche 9 — exclusif, première correspondance</t>
+          <t>branche 9 — exclusif, première correspondance ; motif : « Retenue » (15 876) et « Mare » (7 057) forment l'essentiel du bocage poitevin : petites pièces d'eau, très majoritairement artificielles.</t>
         </is>
       </c>
     </row>
@@ -29750,7 +29766,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>branche 9 — exclusif, première correspondance</t>
+          <t>branche 9 — exclusif, première correspondance ; motif : « Retenue » (15 876) et « Mare » (7 057) forment l'essentiel du bocage poitevin : petites pièces d'eau, très majoritairement artificielles.</t>
         </is>
       </c>
     </row>

--- a/docs/mapping.xlsx
+++ b/docs/mapping.xlsx
@@ -27,11 +27,16 @@
     <sheet name="poste_de_transformation" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="piste_d_aerodrome" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="aerodrome" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="lieu_dit_non_habite" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="construction_ponctuelle" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="pylone" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="detail_hydrographique" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Hors socle" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="commune" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="canton" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="arrondissement" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="epci" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="departement" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="lieu_dit_non_habite" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="construction_ponctuelle" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="pylone" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="detail_hydrographique" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Hors socle" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sommaire'!$A$1:$E$1</definedName>
@@ -54,11 +59,16 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'poste_de_transformation'!$A$1:$E$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'piste_d_aerodrome'!$A$1:$E$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'aerodrome'!$A$1:$E$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'lieu_dit_non_habite'!$A$1:$E$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'construction_ponctuelle'!$A$1:$E$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'pylone'!$A$1:$E$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'detail_hydrographique'!$A$1:$E$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'Hors socle'!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'commune'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'canton'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'arrondissement'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'epci'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'departement'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'lieu_dit_non_habite'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'construction_ponctuelle'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'pylone'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'detail_hydrographique'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'Hors socle'!$A$1:$B$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -500,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -977,92 +987,207 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>lieu_dit_non_habite</t>
+          <t>commune</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>admin_level</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Toponymes de lieux non habités, en points. Mesures sur le département 86, 14 696 points — dont 3 109 bois nommés.</t>
+          <t>Communes → relations `type=boundary` + `boundary=administrative` + `admin_level=8`. Chaque commune garde son propre contour (polygone simple) : les limites communes à deux voisines ne sont pas mutualisées, contrairement à la pratique OSM, mais l'identité `cleabs` reste entière et la géométrie est celle de la BD TOPO. 34 877 communes en France, 13 intersectant Poitiers.</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>construction_ponctuelle</t>
+          <t>canton</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>man_made</t>
+          <t>political_division</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Constructions ponctuelles remarquables : croix, antennes, clochers, éoliennes. Mesures sur le département 86, 4 161 points.</t>
+          <t>Cantons → relations `type=boundary` + `boundary=political` + `political_division=canton`. Circonscriptions électorales départementales, pas des collectivités : OSM les range sous `political`, pas `administrative`. 2 054 en France, 8 intersectant Poitiers.</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>pylone</t>
+          <t>arrondissement</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>admin_level</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Pylônes des lignes haute tension, 3 994 dans la Vienne. Un pylône est un sommet de la ligne qu'il porte : `point_mode: shared` réutilise le nœud de `ligne_electrique` à la même coordonnée, ce qui fait du pylône un vrai nœud de la ligne dans le modèle OSM (`power=tower` sur un nœud de `power=line`).</t>
+          <t>Arrondissements départementaux → relations `type=boundary` + `boundary=administrative` + `admin_level=7`. 332 en France.</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>epci</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>local_authority:FR</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Intercommunalités → relations `type=boundary` + `boundary=local_authority`, la nature juridique dans `local_authority:FR` (convention OSM France). 1 265 EPCI à fiscalité propre en France.</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>departement</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>admin_level</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Départements → relations `type=boundary` + `boundary=administrative` + `admin_level=6`. 101 en France.</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>lieu_dit_non_habite</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Toponymes de lieux non habités, en points. Mesures sur le département 86, 14 696 points — dont 3 109 bois nommés.</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>construction_ponctuelle</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>man_made</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Constructions ponctuelles remarquables : croix, antennes, clochers, éoliennes. Mesures sur le département 86, 4 161 points.</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>pylone</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Pylônes des lignes haute tension, 3 994 dans la Vienne. Un pylône est un sommet de la ligne qu'il porte : `point_mode: shared` réutilise le nœud de `ligne_electrique` à la même coordonnée, ce qui fait du pylône un vrai nœud de la ligne dans le modèle OSM (`power=tower` sur un nœud de `power=line`).</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>detail_hydrographique</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>natural</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Points d'eau remarquables : sources, fontaines, lavoirs, citernes. Mesures sur le département 86, 2 906 points.</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D29" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E29" s="2" t="n">
         <v>21</v>
       </c>
     </row>
@@ -16913,6 +17038,3564 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Champ BD Topo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Valeur / condition</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Tag OSM</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Valeur OSM</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Remarque</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>(toujours)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>IGN BD TOPO® 3.5</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>cleabs</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>ref:FR:IGN:cleabs</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>{cleabs}</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>(toujours)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>administrative</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>(toujours)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>admin_level</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>nom_officiel</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D6" s="2">
+        <f> valeur source</f>
+        <v/>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>code_insee</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>ref:INSEE</t>
+        </is>
+      </c>
+      <c r="D7" s="2">
+        <f> valeur source</f>
+        <v/>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>code_siren</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>ref:FR:SIREN</t>
+        </is>
+      </c>
+      <c r="D8" s="2">
+        <f> valeur source</f>
+        <v/>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>code_postal</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>postal_code</t>
+        </is>
+      </c>
+      <c r="D9" s="2">
+        <f> valeur source</f>
+        <v/>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="D10" s="2">
+        <f> valeur source</f>
+        <v/>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>motif : Population légale publiée par l'INSEE et reprise par la BD TOPO ; OSM attend l'année du recensement (`population:date`) et l'organisme (`source:population`) pour qu'elle soit interprétable. ; si population &gt; 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>date_du_recensement</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>population:date</t>
+        </is>
+      </c>
+      <c r="D11" s="2">
+        <f> valeur source</f>
+        <v/>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>motif : Population légale publiée par l'INSEE et reprise par la BD TOPO ; OSM attend l'année du recensement (`population:date`) et l'organisme (`source:population`) pour qu'elle soit interprétable. ; si population &gt; 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>organisme_recenseur</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>source:population</t>
+        </is>
+      </c>
+      <c r="D12" s="2">
+        <f> valeur source</f>
+        <v/>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>motif : Population légale publiée par l'INSEE et reprise par la BD TOPO ; OSM attend l'année du recensement (`population:date`) et l'organisme (`source:population`) pour qu'elle soit interprétable. ; si population &gt; 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>chef_lieu_d_arrondissement</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>bdtopo:chef_lieu_d_arrondissement</t>
+        </is>
+      </c>
+      <c r="D13" s="2">
+        <f> valeur source</f>
+        <v/>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>ignoré si valeur ∈ {False}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>chef_lieu_de_departement</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>bdtopo:chef_lieu_de_departement</t>
+        </is>
+      </c>
+      <c r="D14" s="2">
+        <f> valeur source</f>
+        <v/>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>ignoré si valeur ∈ {False}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>chef_lieu_de_region</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>bdtopo:chef_lieu_de_region</t>
+        </is>
+      </c>
+      <c r="D15" s="2">
+        <f> valeur source</f>
+        <v/>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>ignoré si valeur ∈ {False}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>chef_lieu_de_collectivite_terr</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>bdtopo:chef_lieu_de_collectivite_terr</t>
+        </is>
+      </c>
+      <c r="D16" s="2">
+        <f> valeur source</f>
+        <v/>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>ignoré si valeur ∈ {False}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>capitale_d_etat</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>bdtopo:capitale_d_etat</t>
+        </is>
+      </c>
+      <c r="D17" s="2">
+        <f> valeur source</f>
+        <v/>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>ignoré si valeur ∈ {False}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>date_creation</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Métadonnée de production IGN, sans équivalent OSM. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>date_modification</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>date_d_apparition</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>date_de_confirmation</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Provenance interne IGN ; le tag `source` porte déjà l'attribution. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>identifiants_sources</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Identifiants du producteur amont. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>methode_d_acquisition_planimetrique</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Qualité de saisie, hors modèle OSM. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>methode_d_acquisition_altimetrique</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Idem, et l'altimétrie est écartée (Z supprimé). ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>precision_planimetrique</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>precision_altimetrique</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>mode_d_obtention_des_coordonnees</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr"/>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>mode_d_obtention_de_l_altitude</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr"/>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>statut</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr"/>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>État de validation interne ; toujours « Validé » en diffusion. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>statut_du_toponyme</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr"/>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Qualité du toponyme (Validé / Collecté), métadonnée de saisie. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>code_du_pays</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr"/>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr"/>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Toujours « FR » sur le territoire traité. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>insee_commune</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr"/>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Rattachement administratif, déductible de la géométrie. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>commune</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr"/>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr"/>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Idem, et redondant avec `insee_commune`. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>identifiant_voie_ban</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Candidat `ref:FR:BAN` — à arbitrer avec l'import adresses. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>id_ban_odonyme</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr"/>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>code_insee_du_canton</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr"/>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Rattachement hiérarchique, porté par la géométrie (le canton est converti).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>code_insee_de_l_arrondissement</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr"/>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr"/>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Idem (l'arrondissement est converti).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>code_insee_de_la_collectivite_terr</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr"/>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Idem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>code_insee_du_departement</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr"/>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr"/>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Idem (le département est converti).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>code_insee_de_la_region</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr"/>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Idem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>codes_siren_des_epci</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr"/>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Idem (l'EPCI est converti, avec son SIREN).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>superficie_cadastrale</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr"/>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Surface en hectares ; OSM ne stocke pas une surface calculable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>lien_vers_chef_lieu</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr"/>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Lien interne vers la zone d'habitation chef-lieu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>liens_vers_autorite_administrative</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr"/>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Lien interne vers la mairie (zone_d_activite_ou_d_interet).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Champ BD Topo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Valeur / condition</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Tag OSM</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Valeur OSM</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Remarque</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>(toujours)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>IGN BD TOPO® 3.5</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>cleabs</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>ref:FR:IGN:cleabs</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>{cleabs}</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>(toujours)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>political</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>(toujours)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>political_division</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>canton</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>nom_officiel</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D6" s="2">
+        <f> valeur source</f>
+        <v/>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>code_insee</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>ref:INSEE</t>
+        </is>
+      </c>
+      <c r="D7" s="2">
+        <f> valeur source</f>
+        <v/>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>composition_du_canton</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>bdtopo:composition_du_canton</t>
+        </is>
+      </c>
+      <c r="D8" s="2">
+        <f> valeur source</f>
+        <v/>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>date_creation</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Métadonnée de production IGN, sans équivalent OSM. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>date_modification</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>date_d_apparition</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>date_de_confirmation</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Provenance interne IGN ; le tag `source` porte déjà l'attribution. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>identifiants_sources</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Identifiants du producteur amont. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>methode_d_acquisition_planimetrique</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Qualité de saisie, hors modèle OSM. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>methode_d_acquisition_altimetrique</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Idem, et l'altimétrie est écartée (Z supprimé). ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>precision_planimetrique</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>precision_altimetrique</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>mode_d_obtention_des_coordonnees</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>mode_d_obtention_de_l_altitude</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>statut</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>État de validation interne ; toujours « Validé » en diffusion. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>statut_du_toponyme</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Qualité du toponyme (Validé / Collecté), métadonnée de saisie. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>code_du_pays</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Toujours « FR » sur le territoire traité. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>insee_commune</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Rattachement administratif, déductible de la géométrie. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>commune</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Idem, et redondant avec `insee_commune`. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>identifiant_voie_ban</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Candidat `ref:FR:BAN` — à arbitrer avec l'import adresses. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>id_ban_odonyme</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>numero_du_canton</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr"/>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Deux derniers chiffres de `code_insee`, redondant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>code_insee_du_departement</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr"/>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Rattachement hiérarchique, porté par la géométrie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>code_insee_de_la_region</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr"/>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Idem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>codes_insee_des_arrondissements</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr"/>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Idem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Champ BD Topo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Valeur / condition</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Tag OSM</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Valeur OSM</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Remarque</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>(toujours)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>IGN BD TOPO® 3.5</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>cleabs</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>ref:FR:IGN:cleabs</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>{cleabs}</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>(toujours)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>administrative</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>(toujours)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>admin_level</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>nom_officiel</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D6" s="2">
+        <f> valeur source</f>
+        <v/>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>code_insee_de_l_arrondissement</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>ref:INSEE</t>
+        </is>
+      </c>
+      <c r="D7" s="2">
+        <f> valeur source</f>
+        <v/>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>date_creation</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Métadonnée de production IGN, sans équivalent OSM. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>date_modification</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>date_d_apparition</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>date_de_confirmation</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Provenance interne IGN ; le tag `source` porte déjà l'attribution. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>identifiants_sources</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Identifiants du producteur amont. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>methode_d_acquisition_planimetrique</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Qualité de saisie, hors modèle OSM. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>methode_d_acquisition_altimetrique</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Idem, et l'altimétrie est écartée (Z supprimé). ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>precision_planimetrique</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>precision_altimetrique</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>mode_d_obtention_des_coordonnees</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>mode_d_obtention_de_l_altitude</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>statut</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>État de validation interne ; toujours « Validé » en diffusion. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>statut_du_toponyme</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Qualité du toponyme (Validé / Collecté), métadonnée de saisie. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>code_du_pays</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Toujours « FR » sur le territoire traité. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>insee_commune</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Rattachement administratif, déductible de la géométrie. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>commune</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Idem, et redondant avec `insee_commune`. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>identifiant_voie_ban</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Candidat `ref:FR:BAN` — à arbitrer avec l'import adresses. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>id_ban_odonyme</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>numero_de_l_arrondissement</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Dernier chiffre de `code_insee_de_l_arrondissement`, redondant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>code_insee_du_departement</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr"/>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Rattachement hiérarchique, porté par la géométrie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>code_insee_de_la_region</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr"/>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Idem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>liens_vers_autorite_administrative</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr"/>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Lien interne vers la sous-préfecture (zone_d_activite_ou_d_interet).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Champ BD Topo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Valeur / condition</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Tag OSM</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Valeur OSM</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Remarque</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>(toujours)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>IGN BD TOPO® 3.5</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>cleabs</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>ref:FR:IGN:cleabs</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>{cleabs}</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>(toujours)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>local_authority</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>nom_officiel</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D5" s="2">
+        <f> valeur source</f>
+        <v/>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>code_siren</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>ref:FR:SIREN</t>
+        </is>
+      </c>
+      <c r="D6" s="2">
+        <f> valeur source</f>
+        <v/>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>nature</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Communauté de communes</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>local_authority:FR</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>nature</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Communauté d'agglomération</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>local_authority:FR</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>nature</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Communauté urbaine</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>local_authority:FR</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>CU</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>nature</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Métropole</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>local_authority:FR</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>metropole</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>nature</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Etablissement public territorial</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>local_authority:FR</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>EPT</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>nature</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>bdtopo:nature</t>
+        </is>
+      </c>
+      <c r="D12" s="2">
+        <f> valeur source</f>
+        <v/>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>date_creation</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Métadonnée de production IGN, sans équivalent OSM. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>date_modification</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>date_d_apparition</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>date_de_confirmation</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Provenance interne IGN ; le tag `source` porte déjà l'attribution. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>identifiants_sources</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Identifiants du producteur amont. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>methode_d_acquisition_planimetrique</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Qualité de saisie, hors modèle OSM. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>methode_d_acquisition_altimetrique</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Idem, et l'altimétrie est écartée (Z supprimé). ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>precision_planimetrique</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>precision_altimetrique</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>mode_d_obtention_des_coordonnees</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>mode_d_obtention_de_l_altitude</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>statut</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>État de validation interne ; toujours « Validé » en diffusion. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>statut_du_toponyme</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Qualité du toponyme (Validé / Collecté), métadonnée de saisie. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>code_du_pays</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Toujours « FR » sur le territoire traité. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>insee_commune</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr"/>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Rattachement administratif, déductible de la géométrie. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>commune</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr"/>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Idem, et redondant avec `insee_commune`. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>identifiant_voie_ban</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr"/>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Candidat `ref:FR:BAN` — à arbitrer avec l'import adresses. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>id_ban_odonyme</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr"/>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>codes_insee_des_communes_membres</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr"/>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr"/>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Composition, portée par la géométrie (les communes sont converties).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>codes_insee_des_departements_membres</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr"/>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Idem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>liens_vers_autorite_administrative</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr"/>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr"/>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Lien interne vers le siège (zone_d_activite_ou_d_interet).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Champ BD Topo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Valeur / condition</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Tag OSM</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Valeur OSM</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Remarque</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>(toujours)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>IGN BD TOPO® 3.5</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>cleabs</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>ref:FR:IGN:cleabs</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>{cleabs}</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>(toujours)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>administrative</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>(toujours)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>admin_level</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>nom_officiel</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D6" s="2">
+        <f> valeur source</f>
+        <v/>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>code_insee</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>ref:INSEE</t>
+        </is>
+      </c>
+      <c r="D7" s="2">
+        <f> valeur source</f>
+        <v/>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>code_siren</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>(valeur reprise telle quelle)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>ref:FR:SIREN</t>
+        </is>
+      </c>
+      <c r="D8" s="2">
+        <f> valeur source</f>
+        <v/>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>date_creation</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Métadonnée de production IGN, sans équivalent OSM. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>date_modification</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>date_d_apparition</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>date_de_confirmation</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Provenance interne IGN ; le tag `source` porte déjà l'attribution. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>identifiants_sources</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Identifiants du producteur amont. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>methode_d_acquisition_planimetrique</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Qualité de saisie, hors modèle OSM. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>methode_d_acquisition_altimetrique</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Idem, et l'altimétrie est écartée (Z supprimé). ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>precision_planimetrique</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>precision_altimetrique</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>mode_d_obtention_des_coordonnees</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>mode_d_obtention_de_l_altitude</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>statut</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>État de validation interne ; toujours « Validé » en diffusion. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>statut_du_toponyme</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Qualité du toponyme (Validé / Collecté), métadonnée de saisie. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>code_du_pays</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Toujours « FR » sur le territoire traité. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>insee_commune</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Rattachement administratif, déductible de la géométrie. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>commune</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Idem, et redondant avec `insee_commune`. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>identifiant_voie_ban</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Candidat `ref:FR:BAN` — à arbitrer avec l'import adresses. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>id_ban_odonyme</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Idem. ; métadonnée commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>code_insee_de_la_region</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr"/>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Rattachement hiérarchique, porté par la géométrie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>liens_vers_autorite_administrative</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr"/>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>(non converti)</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Lien interne vers la préfecture (zone_d_activite_ou_d_interet).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -17484,7 +21167,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18502,7 +22185,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19048,7 +22731,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20032,109 +23715,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Couche</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Motif</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>haie</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>555 203 lignes dans la Vienne — plus que le réseau routier entier. Les haies sont déjà représentées deux fois dans la BD Topo (cette couche linéaire, et 161 425 polygones dans zone_de_vegetation). Les convertir saturerait iD, qui masque déjà les bâtiments au-delà de quelques centaines par écran. Règle simple (`barrier=hedge`) si l'arbitrage change.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>cours_d_eau</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Agrégation toponymique des tronçons hydrographiques : la convertir dupliquerait leur géométrie. Le toponyme est repris sur les tronçons via `cpx_toponyme_de_cours_d_eau`. Candidat naturel à une relation `type=waterway`, à traiter avec les relations.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>plan_d_eau</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Même logique : agrégation des surfaces hydrographiques, toponyme repris via `cpx_toponyme_de_plan_d_eau`.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>erp</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>8 entités seulement dans la Vienne pour 216 615 en France : la couche n'y est pas alimentée. Rien à convertir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>transport_par_cable</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>2 entités dans la Vienne.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>adresse_ban</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Import adresses à part entière (volumétrie et règles propres), hors socle.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:B1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21687,6 +25267,169 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Couche</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Motif</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>haie</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>555 203 lignes dans la Vienne — plus que le réseau routier entier. Les haies sont déjà représentées deux fois dans la BD Topo (cette couche linéaire, et 161 425 polygones dans zone_de_vegetation). Les convertir saturerait iD, qui masque déjà les bâtiments au-delà de quelques centaines par écran. Règle simple (`barrier=hedge`) si l'arbitrage change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>cours_d_eau</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Agrégation toponymique des tronçons hydrographiques : la convertir dupliquerait leur géométrie. Le toponyme est repris sur les tronçons via `cpx_toponyme_de_cours_d_eau`. Candidat naturel à une relation `type=waterway`, à traiter avec les relations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>plan_d_eau</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Même logique : agrégation des surfaces hydrographiques, toponyme repris via `cpx_toponyme_de_plan_d_eau`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>erp</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>8 entités seulement dans la Vienne pour 216 615 en France : la couche n'y est pas alimentée. Rien à convertir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>transport_par_cable</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2 entités dans la Vienne.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Le contour de Nouvelle-Aquitaine compte 214 524 sommets pour un seul objet (`admin_level=4`) : hors d'échelle pour une démonstration départementale, et il alourdirait la base de démonstration au-delà de ce que GitHub accepte. Règle triviale (`boundary=administrative` + `admin_level=4`) si le périmètre devient national.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>arrondissement_municipal</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Paris, Lyon, Marseille seulement ; aucun dans la Vienne.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>commune_associee_ou_deleguee</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Communes fusionnées (`admin_level=9`) ; à ajouter avec les mêmes règles que `commune` si l'on veut les fractions des communes nouvelles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>collectivite_territoriale</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Confondue avec le département hors statuts particuliers (Corse, Paris, Lyon, outre-mer).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>condominium</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Île des Faisans, seul objet de la couche.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>adresse_ban</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Import adresses à part entière (volumétrie et règles propres), hors socle.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -25566,12 +29309,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>nature, usage_1</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>(toujours)</t>
+          <t>(nature ∈ {Eglise, Chapelle}) et (usage_1 = Religieux)</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -25586,19 +29329,19 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>motif : `nature` donne la forme du bâtiment, `usage_1` atteste l'usage courant : c'est leur conjonction qui justifie `amenity=place_of_worship`, pas la forme seule. all_of: - {nature: [Eglise, Chapelle]} - {usage_1: Religieux}</t>
+          <t>motif : `nature` donne la forme du bâtiment, `usage_1` atteste l'usage courant : c'est leur conjonction qui justifie `amenity=place_of_worship`, pas la forme seule.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>nature, usage_1</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>(toujours)</t>
+          <t>(nature ∈ {Eglise, Chapelle}) et (usage_1 = Religieux)</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -25613,7 +29356,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>motif : `nature` donne la forme du bâtiment, `usage_1` atteste l'usage courant : c'est leur conjonction qui justifie `amenity=place_of_worship`, pas la forme seule. all_of: - {nature: [Eglise, Chapelle]} - {usage_1: Religieux}</t>
+          <t>motif : `nature` donne la forme du bâtiment, `usage_1` atteste l'usage courant : c'est leur conjonction qui justifie `amenity=place_of_worship`, pas la forme seule.</t>
         </is>
       </c>
     </row>
